--- a/data/Buff.xlsx
+++ b/data/Buff.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF26"/>
+  <dimension ref="A1:AF25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -442,46 +442,16 @@
           <t>tag</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>tag</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>tag</t>
-        </is>
-      </c>
       <c r="H1" t="inlineStr">
         <is>
           <t>immunetag</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>immunetag</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>immunetag</t>
-        </is>
-      </c>
       <c r="K1" t="inlineStr">
         <is>
           <t>dispeltag</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>dispeltag</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>dispeltag</t>
-        </is>
-      </c>
       <c r="N1" t="inlineStr">
         <is>
           <t>level</t>
@@ -522,11 +492,6 @@
           <t>intervaleffect</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>intervaleffect</t>
-        </is>
-      </c>
       <c r="W1" t="inlineStr">
         <is>
           <t>movement_speed_boost</t>
@@ -547,17 +512,7 @@
           <t>subbuff</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>subbuff</t>
-        </is>
-      </c>
       <c r="AB1" t="inlineStr">
-        <is>
-          <t>targetsubbuff</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
         <is>
           <t>targetsubbuff</t>
         </is>
@@ -584,6 +539,11 @@
           <t>uint32</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>int32</t>
+        </is>
+      </c>
       <c r="C2" t="inlineStr">
         <is>
           <t>uint32</t>
@@ -596,127 +556,82 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>set&lt;string&gt;</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>set&lt;string&gt;</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>set&lt;string&gt;</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>uint32</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>uint32</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>uint32</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>uint32</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>uint32</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>repeated double</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
           <t>string</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>double</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>double</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>double</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>double</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>double</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>double</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>uint32</t>
+          <t>repeated uint32</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>uint32</t>
+          <t>repeated uint32</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -736,268 +651,146 @@
       </c>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>designer</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>set</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>set</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>set</t>
+          <t>common</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>set</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>set</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>set</t>
+          <t>common</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>set</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>set</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>set</t>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>common</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>repeated</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>repeated</t>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>common</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>repeated</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>repeated</t>
+          <t>common</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>repeated</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>repeated</t>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>common</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>designer</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>common</t>
+          <t>multi</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>common</t>
+          <t>expr:double expr_params:level,health</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>common</t>
+          <t>expr:double</t>
         </is>
       </c>
     </row>
     <row r="5">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>强制没有施法者</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
-        <is>
-          <t>multi</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>expr:double expr_params:level,health</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>expr:double</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>强制没有施法者</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
         <is>
           <t>#pragma once
 enum eBuffType {
@@ -1035,140 +828,213 @@
 };</t>
         </is>
       </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Slow:减速</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>免疫tag</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>驱散tag</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>等级</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>最大层数</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>无限时长</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>持续时间</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>强制打断</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>间隔时间</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>间隔时间</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>间隔时间</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>移动速度加成</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>移速降低</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>持续恢复公式</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>子buff</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>子buff</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>若在过去s能命中</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>生效次数</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>额外物理伤害</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Slow:减速</t>
+          <t>Metal</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Control</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>免疫tag</t>
+          <t>Wood</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>免疫tag</t>
+          <t>None</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>免疫tag</t>
+          <t>Control</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>驱散tag</t>
+          <t>Wood</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>驱散tag</t>
+          <t>None</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>驱散tag</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>等级</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>最大层数</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>无限时长</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>持续时间</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>强制打断</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>间隔时间</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>间隔时间</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>间隔时间</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>间隔时间</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>移动速度加成</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>移速降低</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>持续恢复公式</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>子buff</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>子buff</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>子buff</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>子buff</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>若在过去s能命中</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>生效次数</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>额外物理伤害</t>
-        </is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>10</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -1178,7 +1044,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Metal</t>
+          <t>Wood</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1188,7 +1054,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Wood</t>
+          <t>Water</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1203,7 +1069,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Wood</t>
+          <t>Water</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1232,10 +1098,10 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -1276,7 +1142,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -1286,7 +1152,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Wood</t>
+          <t>Water</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1296,7 +1162,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>None</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1311,7 +1177,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>None</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1384,7 +1250,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
@@ -1394,7 +1260,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1404,14 +1270,14 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
+          <t>Earth</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
           <t>None</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="J9" t="inlineStr">
         <is>
           <t>Control</t>
@@ -1419,7 +1285,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Earth</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1492,17 +1358,17 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Earth</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1512,7 +1378,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Earth</t>
+          <t>Metal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1527,7 +1393,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Earth</t>
+          <t>Metal</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1541,10 +1407,10 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="O10" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -1600,7 +1466,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
@@ -1610,7 +1476,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Earth</t>
+          <t>Metal</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1620,7 +1486,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Metal</t>
+          <t>Wood</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1635,7 +1501,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Metal</t>
+          <t>Wood</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1708,7 +1574,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
@@ -1718,7 +1584,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Metal</t>
+          <t>Wood</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1728,7 +1594,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Wood</t>
+          <t>Control</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1743,7 +1609,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Wood</t>
+          <t>Control</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1816,7 +1682,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
@@ -1826,7 +1692,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Wood</t>
+          <t>Metal</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1924,7 +1790,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
@@ -1934,7 +1800,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Metal</t>
+          <t>Wood</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -2032,7 +1898,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
@@ -2042,7 +1908,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Wood</t>
+          <t>Water</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -2140,7 +2006,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
@@ -2150,7 +2016,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2248,7 +2114,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
@@ -2258,7 +2124,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Earth</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2356,52 +2222,22 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>移速降低</t>
+        </is>
       </c>
       <c r="C18" t="n">
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Earth</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>Control</t>
+          <t>MovementSpeedReduction</t>
         </is>
       </c>
       <c r="N18" t="n">
@@ -2435,7 +2271,7 @@
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Y18" t="n">
         <v>0</v>
@@ -2464,20 +2300,20 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>移速降低</t>
+          <t>移除移速降低</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
-      </c>
-      <c r="E19" t="inlineStr">
+        <v>35</v>
+      </c>
+      <c r="K19" t="inlineStr">
         <is>
           <t>MovementSpeedReduction</t>
         </is>
@@ -2513,7 +2349,7 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
         <v>0</v>
@@ -2542,20 +2378,20 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>移除移速降低</t>
+          <t>免疫所有移速降低效果</t>
         </is>
       </c>
       <c r="C20" t="n">
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>35</v>
-      </c>
-      <c r="K20" t="inlineStr">
+        <v>34</v>
+      </c>
+      <c r="H20" t="inlineStr">
         <is>
           <t>MovementSpeedReduction</t>
         </is>
@@ -2570,7 +2406,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -2620,18 +2456,18 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>免疫所有移速降低效果</t>
+          <t>移动速度加成</t>
         </is>
       </c>
       <c r="C21" t="n">
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -2666,7 +2502,7 @@
         <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2698,22 +2534,22 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>移动速度加成</t>
+          <t>每秒回复自身1.3%已损失生命值（随等级成长）</t>
         </is>
       </c>
       <c r="C22" t="n">
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>13</v>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>MovementSpeedReduction</t>
+        <v>42</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>HealthRegenerationBasedOnLostHealth</t>
         </is>
       </c>
       <c r="N22" t="n">
@@ -2723,16 +2559,16 @@
         <v>100</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -2749,8 +2585,10 @@
       <c r="X22" t="n">
         <v>0</v>
       </c>
-      <c r="Y22" t="n">
-        <v>0</v>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>0.013*level*health</t>
+        </is>
       </c>
       <c r="Z22" t="n">
         <v>0</v>
@@ -2776,22 +2614,22 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>每秒回复自身1.3%已损失生命值（随等级成长）</t>
+          <t>若在过去5秒内，没有受到伤害或者被敌方英雄技能命中</t>
         </is>
       </c>
       <c r="C23" t="n">
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>HealthRegenerationBasedOnLostHealth</t>
+          <t>NoDamageOrSkillHitInLastSeconds</t>
         </is>
       </c>
       <c r="N23" t="n">
@@ -2801,10 +2639,10 @@
         <v>100</v>
       </c>
       <c r="P23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -2827,16 +2665,14 @@
       <c r="X23" t="n">
         <v>0</v>
       </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>0.013*level*health</t>
-        </is>
+      <c r="Y23" t="n">
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AB23" t="n">
         <v>0</v>
@@ -2845,7 +2681,7 @@
         <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE23" t="n">
         <v>0</v>
@@ -2856,22 +2692,22 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>若在过去5秒内，没有受到伤害或者被敌方英雄技能命中</t>
+          <t>强化下一次普攻，以造成额外66物理伤害</t>
         </is>
       </c>
       <c r="C24" t="n">
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>NoDamageOrSkillHitInLastSeconds</t>
+          <t>NextBasicAttack</t>
         </is>
       </c>
       <c r="N24" t="n">
@@ -2914,13 +2750,13 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
         <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AD24" t="n">
         <v>5</v>
@@ -2929,16 +2765,16 @@
         <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>强化下一次普攻，以造成额外66物理伤害</t>
+          <t xml:space="preserve"> 沉默目标1.5秒</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -2949,7 +2785,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>NextBasicAttack</t>
+          <t>Silence</t>
         </is>
       </c>
       <c r="N25" t="n">
@@ -2998,93 +2834,15 @@
         <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
         <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>20</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 沉默目标1.5秒</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>0</v>
-      </c>
-      <c r="D26" t="n">
-        <v>36</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Silence</t>
-        </is>
-      </c>
-      <c r="N26" t="n">
-        <v>100</v>
-      </c>
-      <c r="O26" t="n">
-        <v>100</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>5</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="n">
-        <v>1</v>
-      </c>
-      <c r="T26" t="n">
-        <v>0</v>
-      </c>
-      <c r="U26" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" t="n">
-        <v>0</v>
-      </c>
-      <c r="W26" t="n">
-        <v>20</v>
-      </c>
-      <c r="X26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF26" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/Buff.xlsx
+++ b/data/Buff.xlsx
@@ -429,12 +429,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>nocaster</t>
+          <t>no_caster</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>bufftype</t>
+          <t>buff_type</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
@@ -444,12 +444,12 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>immunetag</t>
+          <t>immune_tag</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>dispeltag</t>
+          <t>dispel_tag</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
@@ -459,12 +459,12 @@
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>maxlayer</t>
+          <t>max_layer</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>infiniteduration</t>
+          <t>infinite_duration</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
@@ -474,7 +474,7 @@
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>forceinterrupt</t>
+          <t>force_interrupt</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
@@ -484,12 +484,12 @@
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>intervalcount</t>
+          <t>interval_count</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>intervaleffect</t>
+          <t>interval_effect</t>
         </is>
       </c>
       <c r="W1" t="inlineStr">
@@ -504,22 +504,22 @@
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>healthregeneration</t>
+          <t>health_regeneration</t>
         </is>
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>subbuff</t>
+          <t>sub_buff</t>
         </is>
       </c>
       <c r="AB1" t="inlineStr">
         <is>
-          <t>targetsubbuff</t>
+          <t>target_sub_buff</t>
         </is>
       </c>
       <c r="AD1" t="inlineStr">
         <is>
-          <t>nodamageorskillhitinlastseconds</t>
+          <t>combat_idle_seconds</t>
         </is>
       </c>
       <c r="AE1" t="inlineStr">
@@ -529,7 +529,7 @@
       </c>
       <c r="AF1" t="inlineStr">
         <is>
-          <t>bonusdamage</t>
+          <t>bonus_damage</t>
         </is>
       </c>
     </row>
